--- a/history.xlsx
+++ b/history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I46"/>
+  <dimension ref="A1:I47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2125,6 +2125,43 @@
         </is>
       </c>
     </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>46</v>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Muthulakshmi</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>IMG_20260103_133052.jpg</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>0.853</v>
+      </c>
+      <c r="E47" t="n">
+        <v>0.897</v>
+      </c>
+      <c r="F47" t="n">
+        <v>0.875</v>
+      </c>
+      <c r="G47" t="n">
+        <v>87.5</v>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>Genuine</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>11-04-2026 00:41</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/history.xlsx
+++ b/history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I47"/>
+  <dimension ref="A1:I48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2162,6 +2162,43 @@
         </is>
       </c>
     </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>47</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Muthulakshmi</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>IMG_20260103_133609.jpg</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>0.829</v>
+      </c>
+      <c r="E48" t="n">
+        <v>0.841</v>
+      </c>
+      <c r="F48" t="n">
+        <v>0.835</v>
+      </c>
+      <c r="G48" t="n">
+        <v>83.5</v>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>Forged</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>11-04-2026 01:02</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
